--- a/天猫近3月数据_分析结果/天猫利润分析_干净汇报版.xlsx
+++ b/天猫近3月数据_分析结果/天猫利润分析_干净汇报版.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,21 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -93,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +130,12 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,6 +176,29 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,8 +567,8 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -541,156 +580,218 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天猫近3个月利润分析 · 干净汇报版</t>
-        </is>
-      </c>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>天猫利润分析 · 领导一页纸</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>主口径：ID周损益 · 净利润(推广后)｜周次：5.11–8.2（9个已校验单周）｜单位：元</t>
-        </is>
-      </c>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>口径：ID周损益｜推广后净利润｜5.11–8.2</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>店铺周报仅作附录对照，不与ID成交金额直接混比</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>一、核心结论</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="n"/>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>亏在大链接：量掉的时候利润掉，量回来时又被推广费吃掉；大大包不是主因。</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>核心结论</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>结论1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>最好周为 7.6-7.12（推广后 -4,109）。之后两周回落：7.13 -5,182（-1,073），7.20 -5,614（-432）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>近三个月一直在亏；最好一周是7.6（约-4100），之后又往下掉。</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>结论2</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>7.6→7.13 主因是推广前利润下降（随成交回落）。拖累TOP3：668566625747 袋面主链接（-666）、649369494424 24包经典/牛系列（-211）、648600900806 30包（-202）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>这波回落不是大大包的问题，主责在大链接：先是袋面主链销量掉，后是袋面次链推广加太猛。</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>结论3</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>7.13→7.20 更突出推广费上升。恶化最大：649361890551 袋面次链接（推广后 -259，推广费 +529）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>结构上，袋面主/次链 + 杯面主链长期贡献大部分亏损；巴东新链接也在持续失血。</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>结论4</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>每周绝对亏损长期集中在袋面次链接、袋面主链接、杯面主链接；巴东牛肉等新链接持续大额亏损。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>结论5</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>原味大大包：推广前有利润，但推广后净贡献弱，不是近周回落第一责任。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>结论6</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>5.11→7.27 整段：成交 118,254→107,468（-9.1%），推广后 -6,308→-5,109（亏损略收窄）。不是“整段量增利降”。</t>
-        </is>
-      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>要抓三件事：控主链投产、砍低效推广、巴东减投验证；大大包只控推广侵蚀即可。</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>二、建议</t>
-        </is>
-      </c>
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>请拍板</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1. 优先复盘袋面主链接成交与推广前利润下滑（阶段一）。</t>
-        </is>
-      </c>
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>① 立刻复盘袋面主链接：成交为何掉、推广前利润为何掉。</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2. 压降袋面次链接、30包等低效推广（阶段二）。</t>
-        </is>
-      </c>
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>② 压降袋面次链接、30包等低效花费，先把费率打下来。</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>3. 巴东牛肉单独评估减投/停投。</t>
-        </is>
-      </c>
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>③ 巴东链接减投/停投一周看结果。</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>4. 大大包保留推广前利润，严控推广侵蚀。</t>
-        </is>
-      </c>
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>④ 大大包保留自然利润，严控加投。</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>三、ID周合计趋势（主表）</t>
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>附表：ID周合计（备查）</t>
         </is>
       </c>
     </row>
@@ -1061,6 +1162,12 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
